--- a/currentbuild/StructureDefinition-lmdi-patient.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-patient.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-patient.xlsx
@@ -647,7 +647,7 @@
     <t>FNR</t>
   </si>
   <si>
-    <t>Fødselsnummer</t>
+    <t>National identity number</t>
   </si>
   <si>
     <t>Fødselsnummer for the patient. Fødselsnummer as one of the possible patient identifier, should at least be sent unless there is a reason not to. Reasons for not sending the Fødselsnummer include but are not limited to, research and apps without a contract for processing data.
@@ -763,7 +763,7 @@
 </t>
   </si>
   <si>
-    <t>Fødselsnummeret (11 siffer)</t>
+    <t>National identity number (11 digits)</t>
   </si>
   <si>
     <t>The Norwegian Fødselsnummer</t>
@@ -884,7 +884,7 @@
     <t>DNR</t>
   </si>
   <si>
-    <t>D-nummer</t>
+    <t>D-number</t>
   </si>
   <si>
     <t>The D-nummer of the patient. (assigned by the norwegian Skatteetaten)</t>
@@ -917,7 +917,7 @@
     <t>Patient.identifier:DNR.value</t>
   </si>
   <si>
-    <t>D-nummer (11 siffer)</t>
+    <t>D-number (11 digits)</t>
   </si>
   <si>
     <t>The actual Norwegian D-nummer</t>
@@ -1337,10 +1337,10 @@
 </t>
   </si>
   <si>
-    <t>Kodet verdi for bydel. Kodeverk "Bydelsnummer" (OID 3403)</t>
-  </si>
-  <si>
-    <t>Kodet verdi for bydel. Koder fra kodeverk "Bydelsnummer" (OID 3403) skal benyttes</t>
+    <t>Encoded value for urban district. Code system "Urban district numbers" (OID 3403)</t>
+  </si>
+  <si>
+    <t>Encoded value for urban district. Codes from code system "Urban district numbers" (OID 3403) shall be used.</t>
   </si>
   <si>
     <t>Patient.address.extension:propertyInformation</t>
@@ -1471,7 +1471,7 @@
 kommune</t>
   </si>
   <si>
-    <t>Kommune</t>
+    <t>Municipality</t>
   </si>
   <si>
     <t>Name of the county (norwegian "kommune").
@@ -1528,7 +1528,7 @@
 Territoryfylke</t>
   </si>
   <si>
-    <t>Fylkesnavn</t>
+    <t>County name</t>
   </si>
   <si>
     <t>Name of the norwegian "fylke"). If fylkes-number is required "eiendomsinformasjon" should be used with koded kommune-number.

--- a/currentbuild/StructureDefinition-lmdi-patient.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -647,7 +647,7 @@
     <t>FNR</t>
   </si>
   <si>
-    <t>National identity number</t>
+    <t>Fødselsnummer</t>
   </si>
   <si>
     <t>Fødselsnummer for the patient. Fødselsnummer as one of the possible patient identifier, should at least be sent unless there is a reason not to. Reasons for not sending the Fødselsnummer include but are not limited to, research and apps without a contract for processing data.
@@ -763,7 +763,7 @@
 </t>
   </si>
   <si>
-    <t>National identity number (11 digits)</t>
+    <t>Fødselsnummeret (11 siffer)</t>
   </si>
   <si>
     <t>The Norwegian Fødselsnummer</t>
@@ -884,7 +884,7 @@
     <t>DNR</t>
   </si>
   <si>
-    <t>D-number</t>
+    <t>D-nummer</t>
   </si>
   <si>
     <t>The D-nummer of the patient. (assigned by the norwegian Skatteetaten)</t>
@@ -917,7 +917,7 @@
     <t>Patient.identifier:DNR.value</t>
   </si>
   <si>
-    <t>D-number (11 digits)</t>
+    <t>D-nummer (11 siffer)</t>
   </si>
   <si>
     <t>The actual Norwegian D-nummer</t>
@@ -1337,10 +1337,10 @@
 </t>
   </si>
   <si>
-    <t>Encoded value for urban district. Code system "Urban district numbers" (OID 3403)</t>
-  </si>
-  <si>
-    <t>Encoded value for urban district. Codes from code system "Urban district numbers" (OID 3403) shall be used.</t>
+    <t>Kodet verdi for bydel. Kodeverk "Bydelsnummer" (OID 3403)</t>
+  </si>
+  <si>
+    <t>Kodet verdi for bydel. Koder fra kodeverk "Bydelsnummer" (OID 3403) skal benyttes</t>
   </si>
   <si>
     <t>Patient.address.extension:propertyInformation</t>
@@ -1471,7 +1471,7 @@
 kommune</t>
   </si>
   <si>
-    <t>Municipality</t>
+    <t>Kommune</t>
   </si>
   <si>
     <t>Name of the county (norwegian "kommune").
@@ -1528,7 +1528,7 @@
 Territoryfylke</t>
   </si>
   <si>
-    <t>County name</t>
+    <t>Fylkesnavn</t>
   </si>
   <si>
     <t>Name of the norwegian "fylke"). If fylkes-number is required "eiendomsinformasjon" should be used with koded kommune-number.

--- a/currentbuild/StructureDefinition-lmdi-patient.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-patient.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.3</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
